--- a/GameData/DataTables/Board/PartTable.xlsx
+++ b/GameData/DataTables/Board/PartTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,102 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>PartKind</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>EnergyCost</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TriggerScore</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EnergyCapacity</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EffectCost</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EffectScorePerCell</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EffectScorePerTarget</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PublicEnergyPerEffect</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>BonusScoreFromNth</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>BonusNth</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>RemovesSelf</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>EffectScorePerEnergy</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>PushDistance</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>RayRange</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ChargeThreshold</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SecondaryEffectScore</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SourceHint</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>UseHint</t>
         </is>
       </c>
     </row>
@@ -477,12 +562,97 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -494,22 +664,107 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>可装配零件的基础定义</t>
+          <t>可装配零件的完整静态定义</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>稳定键（P-001~P-020）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>零件显示名称</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>零件大类（占位，取值域待 P0-011 冻结）</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>驱动该零件消耗的能量</t>
+          <t>PartType 数值</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>每次成立触发的触发分</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>零件能量容量</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>单次自身效果消耗的能量</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>每实际推动一格的效果分</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>每个受冲击对象的效果分</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>每次效果产出的公共维修能量</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>达到次数门槛后的额外效果分</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>额外效果分的次数门槛</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>起爆后是否移除本体</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>移除前剩余能量每点的额外效果分</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>单次能力直接推进的格数上限</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>射线搜索或延伸距离</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>蓄量释放阈值</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>次生效果分</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>解锁阶段</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>来源提示</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>一句话功能提示</t>
         </is>
       </c>
     </row>
@@ -519,14 +774,1498 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>铜制齿轮</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>惯性撞锤</t>
+        </is>
       </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>S0 开店教学</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>工作台第一段：先完成一次移动碰撞。</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>把普通碰撞变成下一次位移，承担最基础的连锁接力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>计量棘轮</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>S0 开店教学</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>工作台第二段：在撞锤之后展示能量收益。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>把布置出来的重复碰撞转化为维修能量与表现分，提供值得保护的收益中心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P-003</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>爆破线圈</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>S0 开店教学</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>工作台最后一段：接上爆破与脆裂隔板。</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>同时触发多个邻接对象、拆开局面，形成连锁爆发点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P-004</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>换向齿轮</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>S1 红鞋首案</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>红鞋首关现场演示后永久解锁。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>改变来撞零件的去向，把两条运动路线接起来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P-005</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>弹射簧</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>S3 城市中期</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>第二章普通弹簧维修。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>把一次向下运动重新送回上游，创造回弹接力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P-006</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>分裂铸模</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>S4 画壁筹备</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>第三章加工台进阶委托。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>把值得利用的一枚普通件变成两枚，主动扩大连锁规模。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P-007</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>储料胃袋</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>S3 城市中期</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>穿墙案完成后的回收试机。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>先把零件收起来，等路线合适再吐出，改变连锁时机。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>P-008</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>吞料炉</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>S3 城市中期</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>第二章仓库整理委托。</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>牺牲普通件清理空间，把拥堵转成当前作业的能量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>P-009</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>交换拨叉</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>S4 画壁筹备</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>风月案完成后工作台演示。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>在连锁进行中交换两枚对象，改变后续触发位置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>P-010</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>旋涡转子</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>S4 画壁筹备</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>交换拨叉试机后六邻格重排。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>整体重排六邻格，让一圈零件一起换到新位置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>P-011</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>蓄能飞轮</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>S2 街区初期</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>扫帚初次处理后的工作台试机。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>把分散的小碰撞积成一次大释放，承接跨拍准备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>P-012</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>导电桥</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>13</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>S3 城市中期</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>猴爪案调查准备。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>让隔着空隙的设备互相触发，并维持故事需要的通信线路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>P-013</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>照明棱镜</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>S2 街区初期</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>画皮案识别环节。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>用连锁获得可操作的情报，处理伪装和视野异常。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>P-014</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>铆合钳</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>S1 红鞋首案</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>红鞋准备阶段由周衡借出。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>把连锁能量花在具体修复目标上，连接输出与故事推进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>P-015</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>叩击音叉</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>S2 街区初期</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>裂口女案白天准备后段。</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>把碰撞转成敲门、呼应和引导，支撑声音类挑战。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>P-016</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>排水叶轮</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>S2 街区初期</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>扫帚案前段现场提供。</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>把积压水负荷转成排水与动力，为水灾连锁提供核心转换。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>P-017</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>缓冲囊</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>S4 画壁筹备</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>画像案前段现场提供。</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>承接可转移的设备负荷，为集中释放争取空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>P-018</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>校准探针</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>S3 城市中期</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>穿墙案白天调查。</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>用一次低成本试探确定出口或目标关系，同时承担设备校准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>19</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>P-019</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>磁吸牵引器</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>S2 街区初期</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>裂口女案白天车灯委托。</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>主动把远处一个对象拉近，接上本来碰不到的连锁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>P-020</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>接力电池</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>S2 街区初期</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>画皮完成后的白天工具维修。</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>延长关键器械的工作次数，让持续零件支撑更长连锁。</t>
+        </is>
       </c>
     </row>
   </sheetData>
